--- a/KakeiboAppBackEnd/src/main/resources/textfile/b_詳細設計/画面設計/個別情報画面/個別収支情報画面_詳細.xlsx
+++ b/KakeiboAppBackEnd/src/main/resources/textfile/b_詳細設計/画面設計/個別情報画面/個別収支情報画面_詳細.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjk037_\Desktop\学習用\家計管理アプリ\b_詳細設計\画面設計\個別情報画面\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B769C9FE-DCEB-4ECA-9DE1-E03418F70F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE235067-DC90-47A4-8FCA-9CD2E9C90D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15255" yWindow="0" windowWidth="13860" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13410" yWindow="150" windowWidth="13860" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="機能" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
   <si>
     <t>画面表示時の初期処理</t>
     <rPh sb="0" eb="4">
@@ -56,16 +56,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「カテゴリ」欄にデータのcategoryを入力する</t>
-    <rPh sb="6" eb="7">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>「金額」にデータのamountを入力する</t>
     <rPh sb="1" eb="3">
       <t>キンガク</t>
@@ -103,35 +93,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>空白の新規KakeiboDTOオブジェクトが、データ更新情報の</t>
-    <rPh sb="0" eb="2">
-      <t>クウハク</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シンキ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>登録対象として作成される</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>KakeiboDTOに新しい日付が登録される</t>
     <rPh sb="11" eb="12">
       <t>アタラ</t>
@@ -511,6 +472,100 @@
     <t>KakeiboDTOの削除フラグが9になる</t>
     <rPh sb="11" eb="13">
       <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「収支分類」に、データのinOutが"IN"であれば「収入」、</t>
+    <rPh sb="1" eb="3">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ブンルイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シュウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>"OUT"であれば「支出」を表示する</t>
+    <rPh sb="10" eb="12">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「カテゴリー」欄にデータのcategoryを入力する</t>
+    <rPh sb="7" eb="8">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「編集」ボタンを押す</t>
+    <rPh sb="1" eb="3">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「カテゴリー」欄が「収支分類」に対応したドロップダウンになる</t>
+    <rPh sb="7" eb="8">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ブンルイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「収支分類」が押下するたびに表示の切り替わるボタンになる</t>
+    <rPh sb="1" eb="3">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ブンルイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「金額」がnumber型の入力エリアになる</t>
+    <rPh sb="1" eb="3">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ニュウリョク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -535,12 +590,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -555,8 +616,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -837,267 +899,289 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:B72"/>
+  <dimension ref="B2:D78"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="2" spans="2:2">
-      <c r="B2" t="s">
+    <row r="2" spans="2:4">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="2:2">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="4" spans="2:4">
       <c r="B4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:2">
+    <row r="5" spans="2:4">
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
       <c r="B6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:2">
-      <c r="B7" t="s">
+    <row r="9" spans="2:4">
+      <c r="B9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:2">
-      <c r="B8" t="s">
+    <row r="10" spans="2:4">
+      <c r="B10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:2">
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2">
+    <row r="12" spans="2:4">
       <c r="B12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
       <c r="B14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
       <c r="B15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" t="s">
-        <v>11</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" t="s">
-        <v>28</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>14</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2">
-      <c r="B66" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" t="s">
-        <v>46</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
